--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K575"/>
+  <dimension ref="A1:K577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22467,7 +22467,7 @@
         <v>460.21</v>
       </c>
       <c r="C567" t="n">
-        <v>470.99</v>
+        <v>475.89</v>
       </c>
       <c r="D567" t="n">
         <v>398.68</v>
@@ -22506,7 +22506,7 @@
         <v>454.66</v>
       </c>
       <c r="C568" t="n">
-        <v>459.58</v>
+        <v>475.89</v>
       </c>
       <c r="D568" t="n">
         <v>397.45</v>
@@ -22545,7 +22545,7 @@
         <v>450.06</v>
       </c>
       <c r="C569" t="n">
-        <v>451.58</v>
+        <v>475.89</v>
       </c>
       <c r="D569" t="n">
         <v>395.52</v>
@@ -22584,7 +22584,7 @@
         <v>455.86</v>
       </c>
       <c r="C570" t="n">
-        <v>453.25</v>
+        <v>483.41</v>
       </c>
       <c r="D570" t="n">
         <v>395.22</v>
@@ -22623,7 +22623,7 @@
         <v>455.12</v>
       </c>
       <c r="C571" t="n">
-        <v>445.38</v>
+        <v>483.41</v>
       </c>
       <c r="D571" t="n">
         <v>394.48</v>
@@ -22662,7 +22662,7 @@
         <v>452.37</v>
       </c>
       <c r="C572" t="n">
-        <v>443.75</v>
+        <v>483.41</v>
       </c>
       <c r="D572" t="n">
         <v>394.43</v>
@@ -22701,7 +22701,7 @@
         <v>452.37</v>
       </c>
       <c r="C573" t="n">
-        <v>443.75</v>
+        <v>483.41</v>
       </c>
       <c r="D573" t="n">
         <v>394.43</v>
@@ -22740,7 +22740,7 @@
         <v>446.67</v>
       </c>
       <c r="C574" t="n">
-        <v>446.31</v>
+        <v>483.41</v>
       </c>
       <c r="D574" t="n">
         <v>390.23</v>
@@ -22779,7 +22779,7 @@
         <v>451.67</v>
       </c>
       <c r="C575" t="n">
-        <v>449.48</v>
+        <v>483.57</v>
       </c>
       <c r="D575" t="n">
         <v>390.23</v>
@@ -22803,6 +22803,84 @@
         <v>393.63</v>
       </c>
       <c r="K575" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>451.17</v>
+      </c>
+      <c r="C576" t="n">
+        <v>477.82</v>
+      </c>
+      <c r="D576" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="E576" t="n">
+        <v>392.28</v>
+      </c>
+      <c r="F576" t="n">
+        <v>391.09</v>
+      </c>
+      <c r="G576" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="H576" t="n">
+        <v>386</v>
+      </c>
+      <c r="I576" t="n">
+        <v>382.79</v>
+      </c>
+      <c r="J576" t="n">
+        <v>393.79</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>453.92</v>
+      </c>
+      <c r="C577" t="n">
+        <v>477.82</v>
+      </c>
+      <c r="D577" t="n">
+        <v>389.77</v>
+      </c>
+      <c r="E577" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="F577" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="G577" t="n">
+        <v>385.7</v>
+      </c>
+      <c r="H577" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="I577" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="J577" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="K577" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22819,7 +22897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B585"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28672,6 +28750,26 @@
       </c>
       <c r="B585" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -28840,28 +28938,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1457011689917063</v>
+        <v>0.1545836642845234</v>
       </c>
       <c r="J2" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K2" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003561723945071149</v>
+        <v>0.004030848706808032</v>
       </c>
       <c r="M2" t="n">
-        <v>14.08564868295377</v>
+        <v>14.09573939373612</v>
       </c>
       <c r="N2" t="n">
-        <v>332.9998325859398</v>
+        <v>332.4227074082233</v>
       </c>
       <c r="O2" t="n">
-        <v>18.24828300377709</v>
+        <v>18.23246300992335</v>
       </c>
       <c r="P2" t="n">
-        <v>435.6673248038542</v>
+        <v>435.5718148114068</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28918,28 +29016,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1670567803869006</v>
+        <v>-0.05234004897347155</v>
       </c>
       <c r="J3" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K3" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002200486422609171</v>
+        <v>0.0002119592094029787</v>
       </c>
       <c r="M3" t="n">
-        <v>21.72579893718521</v>
+        <v>22.17594016668392</v>
       </c>
       <c r="N3" t="n">
-        <v>682.1286528742521</v>
+        <v>699.4276432282503</v>
       </c>
       <c r="O3" t="n">
-        <v>26.11759278483092</v>
+        <v>26.44669437242111</v>
       </c>
       <c r="P3" t="n">
-        <v>451.2981039875828</v>
+        <v>450.033292779633</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28996,28 +29094,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2002756278294765</v>
+        <v>-0.2033127734386645</v>
       </c>
       <c r="J4" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K4" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01669860227193787</v>
+        <v>0.0173201498069715</v>
       </c>
       <c r="M4" t="n">
-        <v>9.182880626229306</v>
+        <v>9.166756813569474</v>
       </c>
       <c r="N4" t="n">
-        <v>131.6161509745062</v>
+        <v>131.2296005621686</v>
       </c>
       <c r="O4" t="n">
-        <v>11.47240824650632</v>
+        <v>11.45554889833606</v>
       </c>
       <c r="P4" t="n">
-        <v>400.9289644567784</v>
+        <v>400.9617566848904</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29074,28 +29172,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.530023332063861</v>
+        <v>-0.5373336480396825</v>
       </c>
       <c r="J5" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K5" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2445990542060211</v>
+        <v>0.2496007616411483</v>
       </c>
       <c r="M5" t="n">
-        <v>5.056051755373732</v>
+        <v>5.073548834772359</v>
       </c>
       <c r="N5" t="n">
-        <v>48.22961817062762</v>
+        <v>48.4559492918515</v>
       </c>
       <c r="O5" t="n">
-        <v>6.944754723575745</v>
+        <v>6.961030763604733</v>
       </c>
       <c r="P5" t="n">
-        <v>415.7997888789803</v>
+        <v>415.8786711711012</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29152,28 +29250,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5523966463347793</v>
+        <v>-0.5605442798504868</v>
       </c>
       <c r="J6" t="n">
+        <v>576</v>
+      </c>
+      <c r="K6" t="n">
         <v>574</v>
       </c>
-      <c r="K6" t="n">
-        <v>572</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3175086899221038</v>
+        <v>0.3226522715156387</v>
       </c>
       <c r="M6" t="n">
-        <v>4.921067660414339</v>
+        <v>4.940935939080846</v>
       </c>
       <c r="N6" t="n">
-        <v>36.79822037032493</v>
+        <v>37.15999177324243</v>
       </c>
       <c r="O6" t="n">
-        <v>6.066153671835633</v>
+        <v>6.09589958687333</v>
       </c>
       <c r="P6" t="n">
-        <v>417.1606101552404</v>
+        <v>417.2480581911906</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29230,28 +29328,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5158616667289531</v>
+        <v>-0.5218824730959541</v>
       </c>
       <c r="J7" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K7" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3142153124110157</v>
+        <v>0.3191109979568054</v>
       </c>
       <c r="M7" t="n">
-        <v>4.475961516118481</v>
+        <v>4.490059228387834</v>
       </c>
       <c r="N7" t="n">
-        <v>32.48308529714928</v>
+        <v>32.63736012371078</v>
       </c>
       <c r="O7" t="n">
-        <v>5.699393414842432</v>
+        <v>5.712911702775633</v>
       </c>
       <c r="P7" t="n">
-        <v>409.0445915918044</v>
+        <v>409.1092807533826</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29308,28 +29406,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3273689413400606</v>
+        <v>-0.3325918543142885</v>
       </c>
       <c r="J8" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K8" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1538276299554979</v>
+        <v>0.1582010488513899</v>
       </c>
       <c r="M8" t="n">
-        <v>4.41708958562069</v>
+        <v>4.423449012372016</v>
       </c>
       <c r="N8" t="n">
-        <v>32.97082083694934</v>
+        <v>33.05653217536471</v>
       </c>
       <c r="O8" t="n">
-        <v>5.742022364720408</v>
+        <v>5.749481035307857</v>
       </c>
       <c r="P8" t="n">
-        <v>402.1203489496644</v>
+        <v>402.1764624354198</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29386,28 +29484,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1852827520449605</v>
+        <v>-0.1959249557706595</v>
       </c>
       <c r="J9" t="n">
+        <v>576</v>
+      </c>
+      <c r="K9" t="n">
         <v>574</v>
       </c>
-      <c r="K9" t="n">
-        <v>572</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0455425114071516</v>
+        <v>0.05003395809365063</v>
       </c>
       <c r="M9" t="n">
-        <v>5.015881141360129</v>
+        <v>5.055622708456421</v>
       </c>
       <c r="N9" t="n">
-        <v>40.35291272830246</v>
+        <v>41.04713924336339</v>
       </c>
       <c r="O9" t="n">
-        <v>6.35239425164264</v>
+        <v>6.406804136491406</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6565458750407</v>
+        <v>402.7707957899099</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29464,28 +29562,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001427655062500791</v>
+        <v>-0.005793802031715828</v>
       </c>
       <c r="J10" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K10" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L10" t="n">
-        <v>4.080170215470247e-06</v>
+        <v>6.67858943649291e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>4.27073524839466</v>
+        <v>4.293589302798322</v>
       </c>
       <c r="N10" t="n">
-        <v>28.03319707782296</v>
+        <v>28.3204292193342</v>
       </c>
       <c r="O10" t="n">
-        <v>5.294638521922244</v>
+        <v>5.32169420573319</v>
       </c>
       <c r="P10" t="n">
-        <v>403.8369746067075</v>
+        <v>403.9146268998905</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29523,7 +29621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K575"/>
+  <dimension ref="A1:K577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61669,7 +61767,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>-36.52892699606783,174.7154598238996</t>
+          <t>-36.52892941755808,174.71551446085496</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -61726,7 +61824,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>-36.52892135735744,174.7153325978557</t>
+          <t>-36.52892941755808,174.71551446085496</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -61783,7 +61881,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>-36.52891740375441,174.7152433946776</t>
+          <t>-36.52892941755808,174.71551446085496</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -61840,7 +61938,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>-36.52891822907458,174.7152620158405</t>
+          <t>-36.528933133755444,174.7155983118605</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -61897,7 +61995,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>-36.528914339665995,174.71517426221894</t>
+          <t>-36.528933133755444,174.7155983118605</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -61954,7 +62052,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>-36.52891353410058,174.71515608707318</t>
+          <t>-36.528933133755444,174.7155983118605</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -62011,7 +62109,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>-36.52891353410058,174.71515608707318</t>
+          <t>-36.528933133755444,174.7155983118605</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -62068,7 +62166,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>-36.52891479928182,174.7151846320875</t>
+          <t>-36.528933133755444,174.7155983118605</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -62125,7 +62223,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>-36.52891636592252,174.7152199788444</t>
+          <t>-36.52893321282283,174.71560009592451</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -62164,6 +62262,120 @@
         </is>
       </c>
       <c r="K575" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-36.52819694805156,174.7152985520411</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-36.528930371321835,174.7155359811258</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-36.52963275669177,174.71452266348246</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-36.53035606558643,174.71430503407709</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-36.53103863671111,174.71407896388465</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-36.53174107149817,174.71391544865693</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-36.53245642457917,174.71373435489423</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-36.53314357376829,174.71351693881525</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-36.533844680434925,174.71359975899836</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-36.52819830710722,174.715329215348</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-36.528930371321835,174.7155359811258</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-36.52962932467038,174.7144924747927</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-36.530350553030566,174.71427566596054</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-36.53103646234845,174.71406390350046</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-36.5317392463649,174.71390043003004</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-36.53245537732262,174.71372743994615</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-36.53314220038133,174.71350218344003</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>-36.53384439961597,174.71358960215593</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K577"/>
+  <dimension ref="A1:K578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22883,6 +22883,45 @@
       <c r="K577" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>453.92</v>
+      </c>
+      <c r="C578" t="n">
+        <v>477.82</v>
+      </c>
+      <c r="D578" t="n">
+        <v>389.77</v>
+      </c>
+      <c r="E578" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="F578" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="G578" t="n">
+        <v>386.61</v>
+      </c>
+      <c r="H578" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="I578" t="n">
+        <v>382.14</v>
+      </c>
+      <c r="J578" t="n">
+        <v>393.51</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28770,6 +28809,16 @@
       </c>
       <c r="B587" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -28938,28 +28987,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1545836642845234</v>
+        <v>0.1594390629795961</v>
       </c>
       <c r="J2" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K2" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004030848706808032</v>
+        <v>0.00429870807036481</v>
       </c>
       <c r="M2" t="n">
-        <v>14.09573939373612</v>
+        <v>14.10339995760111</v>
       </c>
       <c r="N2" t="n">
-        <v>332.4227074082233</v>
+        <v>332.1914662635598</v>
       </c>
       <c r="O2" t="n">
-        <v>18.23246300992335</v>
+        <v>18.22612043918178</v>
       </c>
       <c r="P2" t="n">
-        <v>435.5718148114068</v>
+        <v>435.5194893179711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29016,28 +29065,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05234004897347155</v>
+        <v>-0.04196745328623429</v>
       </c>
       <c r="J3" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002119592094029787</v>
+        <v>0.0001365154082455522</v>
       </c>
       <c r="M3" t="n">
-        <v>22.17594016668392</v>
+        <v>22.18625753740574</v>
       </c>
       <c r="N3" t="n">
-        <v>699.4276432282503</v>
+        <v>699.6915559544287</v>
       </c>
       <c r="O3" t="n">
-        <v>26.44669437242111</v>
+        <v>26.45168342382822</v>
       </c>
       <c r="P3" t="n">
-        <v>450.033292779633</v>
+        <v>449.918101040847</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29094,28 +29143,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2033127734386645</v>
+        <v>-0.205277964871305</v>
       </c>
       <c r="J4" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K4" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0173201498069715</v>
+        <v>0.01770941437565277</v>
       </c>
       <c r="M4" t="n">
-        <v>9.166756813569474</v>
+        <v>9.161094455604513</v>
       </c>
       <c r="N4" t="n">
-        <v>131.2296005621686</v>
+        <v>131.0572249707861</v>
       </c>
       <c r="O4" t="n">
-        <v>11.45554889833606</v>
+        <v>11.44802275376784</v>
       </c>
       <c r="P4" t="n">
-        <v>400.9617566848904</v>
+        <v>400.9830160287971</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29172,28 +29221,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5373336480396825</v>
+        <v>-0.5413996168041952</v>
       </c>
       <c r="J5" t="n">
+        <v>577</v>
+      </c>
+      <c r="K5" t="n">
         <v>576</v>
       </c>
-      <c r="K5" t="n">
-        <v>575</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2496007616411483</v>
+        <v>0.2522178863293378</v>
       </c>
       <c r="M5" t="n">
-        <v>5.073548834772359</v>
+        <v>5.084294704715862</v>
       </c>
       <c r="N5" t="n">
-        <v>48.4559492918515</v>
+        <v>48.61317124638845</v>
       </c>
       <c r="O5" t="n">
-        <v>6.961030763604733</v>
+        <v>6.972314626176048</v>
       </c>
       <c r="P5" t="n">
-        <v>415.8786711711012</v>
+        <v>415.9226411145606</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29250,28 +29299,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5605442798504868</v>
+        <v>-0.5647944760907706</v>
       </c>
       <c r="J6" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K6" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3226522715156387</v>
+        <v>0.3252232291926325</v>
       </c>
       <c r="M6" t="n">
-        <v>4.940935939080846</v>
+        <v>4.951574001767376</v>
       </c>
       <c r="N6" t="n">
-        <v>37.15999177324243</v>
+        <v>37.36256093221051</v>
       </c>
       <c r="O6" t="n">
-        <v>6.09589958687333</v>
+        <v>6.112492203038832</v>
       </c>
       <c r="P6" t="n">
-        <v>417.2480581911906</v>
+        <v>417.2937807773099</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29328,28 +29377,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5218824730959541</v>
+        <v>-0.524770049330437</v>
       </c>
       <c r="J7" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K7" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3191109979568054</v>
+        <v>0.3215247870388821</v>
       </c>
       <c r="M7" t="n">
-        <v>4.490059228387834</v>
+        <v>4.496470988860044</v>
       </c>
       <c r="N7" t="n">
-        <v>32.63736012371078</v>
+        <v>32.70360398871169</v>
       </c>
       <c r="O7" t="n">
-        <v>5.712911702775633</v>
+        <v>5.718706496115331</v>
       </c>
       <c r="P7" t="n">
-        <v>409.1092807533826</v>
+        <v>409.1403761311373</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29406,28 +29455,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3325918543142885</v>
+        <v>-0.334929887256359</v>
       </c>
       <c r="J8" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K8" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1582010488513899</v>
+        <v>0.1602610068738942</v>
       </c>
       <c r="M8" t="n">
-        <v>4.423449012372016</v>
+        <v>4.425736675888901</v>
       </c>
       <c r="N8" t="n">
-        <v>33.05653217536471</v>
+        <v>33.07975372939595</v>
       </c>
       <c r="O8" t="n">
-        <v>5.749481035307857</v>
+        <v>5.751500128609574</v>
       </c>
       <c r="P8" t="n">
-        <v>402.1764624354198</v>
+        <v>402.2016399585856</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29484,28 +29533,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1959249557706595</v>
+        <v>-0.2011742204168099</v>
       </c>
       <c r="J9" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K9" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05003395809365063</v>
+        <v>0.05230535469898578</v>
       </c>
       <c r="M9" t="n">
-        <v>5.055622708456421</v>
+        <v>5.075340771734813</v>
       </c>
       <c r="N9" t="n">
-        <v>41.04713924336339</v>
+        <v>41.38330087488697</v>
       </c>
       <c r="O9" t="n">
-        <v>6.406804136491406</v>
+        <v>6.432985378102998</v>
       </c>
       <c r="P9" t="n">
-        <v>402.7707957899099</v>
+        <v>402.8272810101477</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29562,28 +29611,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.005793802031715828</v>
+        <v>-0.009303096431923303</v>
       </c>
       <c r="J10" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K10" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L10" t="n">
-        <v>6.67858943649291e-05</v>
+        <v>0.0001717202135779194</v>
       </c>
       <c r="M10" t="n">
-        <v>4.293589302798322</v>
+        <v>4.30493248036193</v>
       </c>
       <c r="N10" t="n">
-        <v>28.3204292193342</v>
+        <v>28.45352437226318</v>
       </c>
       <c r="O10" t="n">
-        <v>5.32169420573319</v>
+        <v>5.33418450864452</v>
       </c>
       <c r="P10" t="n">
-        <v>403.9146268998905</v>
+        <v>403.9524507952752</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29621,7 +29670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K577"/>
+  <dimension ref="A1:K578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62381,6 +62430,63 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-36.52819830710722,174.715329215348</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-36.528930371321835,174.7155359811258</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-36.52962932467038,174.7144924747927</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-36.530350553030566,174.71427566596054</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-36.53103646234845,174.71406390350046</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-36.531740467594,174.71391047925826</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-36.53245705625753,174.7137385258154</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-36.533142902564364,174.71350972754158</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>-36.53384459402919,174.71359663381608</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0131/nzd0131.xlsx
+++ b/data/nzd0131/nzd0131.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K578"/>
+  <dimension ref="A1:K580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22815,10 +22815,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>451.17</v>
+        <v>451.67</v>
       </c>
       <c r="C576" t="n">
-        <v>477.82</v>
+        <v>483.57</v>
       </c>
       <c r="D576" t="n">
         <v>392.5</v>
@@ -22854,10 +22854,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>453.92</v>
+        <v>454.69</v>
       </c>
       <c r="C577" t="n">
-        <v>477.82</v>
+        <v>483.57</v>
       </c>
       <c r="D577" t="n">
         <v>389.77</v>
@@ -22893,10 +22893,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>453.92</v>
+        <v>454.69</v>
       </c>
       <c r="C578" t="n">
-        <v>477.82</v>
+        <v>483.57</v>
       </c>
       <c r="D578" t="n">
         <v>389.77</v>
@@ -22920,6 +22920,84 @@
         <v>393.51</v>
       </c>
       <c r="K578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:47+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>454.69</v>
+      </c>
+      <c r="C579" t="n">
+        <v>498.99</v>
+      </c>
+      <c r="D579" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="E579" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="F579" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="G579" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="H579" t="n">
+        <v>386.76</v>
+      </c>
+      <c r="I579" t="n">
+        <v>382.99</v>
+      </c>
+      <c r="J579" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>455.97</v>
+      </c>
+      <c r="C580" t="n">
+        <v>497.93</v>
+      </c>
+      <c r="D580" t="n">
+        <v>394.61</v>
+      </c>
+      <c r="E580" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="F580" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="G580" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="H580" t="n">
+        <v>387.48</v>
+      </c>
+      <c r="I580" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="J580" t="n">
+        <v>394.59</v>
+      </c>
+      <c r="K580" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22936,7 +23014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28819,6 +28897,26 @@
       </c>
       <c r="B588" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28987,28 +29085,28 @@
         <v>0.0155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1594390629795961</v>
+        <v>0.1707052101028618</v>
       </c>
       <c r="J2" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K2" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00429870807036481</v>
+        <v>0.004948343187968995</v>
       </c>
       <c r="M2" t="n">
-        <v>14.10339995760111</v>
+        <v>14.1285710981219</v>
       </c>
       <c r="N2" t="n">
-        <v>332.1914662635598</v>
+        <v>331.961294136609</v>
       </c>
       <c r="O2" t="n">
-        <v>18.22612043918178</v>
+        <v>18.21980499721688</v>
       </c>
       <c r="P2" t="n">
-        <v>435.5194893179711</v>
+        <v>435.3977166021505</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29065,28 +29163,28 @@
         <v>0.015</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04196745328623429</v>
+        <v>-0.0007944964620516708</v>
       </c>
       <c r="J3" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K3" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001365154082455522</v>
+        <v>4.857690949489069e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>22.18625753740574</v>
+        <v>22.30341358772922</v>
       </c>
       <c r="N3" t="n">
-        <v>699.6915559544287</v>
+        <v>707.777281882738</v>
       </c>
       <c r="O3" t="n">
-        <v>26.45168342382822</v>
+        <v>26.60408393241041</v>
       </c>
       <c r="P3" t="n">
-        <v>449.918101040847</v>
+        <v>449.4597577326343</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29143,28 +29241,28 @@
         <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.205277964871305</v>
+        <v>-0.2064310305093378</v>
       </c>
       <c r="J4" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01770941437565277</v>
+        <v>0.01803871344493302</v>
       </c>
       <c r="M4" t="n">
-        <v>9.161094455604513</v>
+        <v>9.135272713485442</v>
       </c>
       <c r="N4" t="n">
-        <v>131.0572249707861</v>
+        <v>130.6137339922638</v>
       </c>
       <c r="O4" t="n">
-        <v>11.44802275376784</v>
+        <v>11.42863657626157</v>
       </c>
       <c r="P4" t="n">
-        <v>400.9830160287971</v>
+        <v>400.9955209071682</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29221,28 +29319,28 @@
         <v>0.0217</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5413996168041952</v>
+        <v>-0.5503335791940492</v>
       </c>
       <c r="J5" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2522178863293378</v>
+        <v>0.2576217913387571</v>
       </c>
       <c r="M5" t="n">
-        <v>5.084294704715862</v>
+        <v>5.109596967016431</v>
       </c>
       <c r="N5" t="n">
-        <v>48.61317124638845</v>
+        <v>49.02738467398021</v>
       </c>
       <c r="O5" t="n">
-        <v>6.972314626176048</v>
+        <v>7.00195577492319</v>
       </c>
       <c r="P5" t="n">
-        <v>415.9226411145606</v>
+        <v>416.0195584305928</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29299,28 +29397,28 @@
         <v>0.0256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5647944760907706</v>
+        <v>-0.5726652200151977</v>
       </c>
       <c r="J6" t="n">
+        <v>579</v>
+      </c>
+      <c r="K6" t="n">
         <v>577</v>
       </c>
-      <c r="K6" t="n">
-        <v>575</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3252232291926325</v>
+        <v>0.3302964650016021</v>
       </c>
       <c r="M6" t="n">
-        <v>4.951574001767376</v>
+        <v>4.969653608861649</v>
       </c>
       <c r="N6" t="n">
-        <v>37.36256093221051</v>
+        <v>37.6935249360377</v>
       </c>
       <c r="O6" t="n">
-        <v>6.112492203038832</v>
+        <v>6.139505268019378</v>
       </c>
       <c r="P6" t="n">
-        <v>417.2937807773099</v>
+        <v>417.3787140944759</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29377,28 +29475,28 @@
         <v>0.0267</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.524770049330437</v>
+        <v>-0.5294769148407557</v>
       </c>
       <c r="J7" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K7" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3215247870388821</v>
+        <v>0.3259983526363207</v>
       </c>
       <c r="M7" t="n">
-        <v>4.496470988860044</v>
+        <v>4.504238224354654</v>
       </c>
       <c r="N7" t="n">
-        <v>32.70360398871169</v>
+        <v>32.7563900206298</v>
       </c>
       <c r="O7" t="n">
-        <v>5.718706496115331</v>
+        <v>5.723319842593964</v>
       </c>
       <c r="P7" t="n">
-        <v>409.1403761311373</v>
+        <v>409.1912150301908</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29455,28 +29553,28 @@
         <v>0.0305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.334929887256359</v>
+        <v>-0.3390389885245414</v>
       </c>
       <c r="J8" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K8" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1602610068738942</v>
+        <v>0.1641001753804635</v>
       </c>
       <c r="M8" t="n">
-        <v>4.425736675888901</v>
+        <v>4.427850749712631</v>
       </c>
       <c r="N8" t="n">
-        <v>33.07975372939595</v>
+        <v>33.0903147384883</v>
       </c>
       <c r="O8" t="n">
-        <v>5.751500128609574</v>
+        <v>5.752418164432093</v>
       </c>
       <c r="P8" t="n">
-        <v>402.2016399585856</v>
+        <v>402.2460260689163</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29533,28 +29631,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2011742204168099</v>
+        <v>-0.2105900002623302</v>
       </c>
       <c r="J9" t="n">
+        <v>579</v>
+      </c>
+      <c r="K9" t="n">
         <v>577</v>
       </c>
-      <c r="K9" t="n">
-        <v>575</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.05230535469898578</v>
+        <v>0.0565930095784869</v>
       </c>
       <c r="M9" t="n">
-        <v>5.075340771734813</v>
+        <v>5.110062388272322</v>
       </c>
       <c r="N9" t="n">
-        <v>41.38330087488697</v>
+        <v>41.89658258321624</v>
       </c>
       <c r="O9" t="n">
-        <v>6.432985378102998</v>
+        <v>6.472756953819311</v>
       </c>
       <c r="P9" t="n">
-        <v>402.8272810101477</v>
+        <v>402.9289174872147</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29611,28 +29709,28 @@
         <v>0.0353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009303096431923303</v>
+        <v>-0.01577558689565636</v>
       </c>
       <c r="J10" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K10" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001717202135779194</v>
+        <v>0.0004920057226761587</v>
       </c>
       <c r="M10" t="n">
-        <v>4.30493248036193</v>
+        <v>4.32495936115027</v>
       </c>
       <c r="N10" t="n">
-        <v>28.45352437226318</v>
+        <v>28.66542195863384</v>
       </c>
       <c r="O10" t="n">
-        <v>5.33418450864452</v>
+        <v>5.354009895268577</v>
       </c>
       <c r="P10" t="n">
-        <v>403.9524507952752</v>
+        <v>404.022432328902</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29670,7 +29768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K578"/>
+  <dimension ref="A1:K580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62324,12 +62422,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>-36.52819694805156,174.7152985520411</t>
+          <t>-36.52819719515318,174.71530412718775</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>-36.528930371321835,174.7155359811258</t>
+          <t>-36.52893321282283,174.71560009592451</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -62381,12 +62479,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>-36.52819830710722,174.715329215348</t>
+          <t>-36.528198687641385,174.715337801074</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>-36.528930371321835,174.7155359811258</t>
+          <t>-36.52893321282283,174.71560009592451</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -62438,12 +62536,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>-36.52819830710722,174.715329215348</t>
+          <t>-36.528198687641385,174.715337801074</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>-36.528930371321835,174.7155359811258</t>
+          <t>-36.52893321282283,174.71560009592451</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -62482,6 +62580,120 @@
         </is>
       </c>
       <c r="K578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:05:47+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-36.528198687641385,174.715337801074</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-36.528940832816396,174.7157720351054</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-36.529633259551396,174.71452708673388</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-36.53034783758367,174.71426119944533</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-36.53103639886338,174.71406346378123</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-36.53174127279952,174.7139171051232</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-36.53245768793574,174.7137426967366</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-36.53314378029249,174.7135191576687</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>-36.5338446927786,174.71360020545296</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-36.528199320216274,174.71535207344994</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>-36.52894030901159,174.71576021567975</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>-36.52963540927445,174.71454599613438</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>-36.53034783758367,174.71426119944533</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>-36.531038922393655,174.7140809426213</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-36.53174352737301,174.7139356575456</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-36.5324588847993,174.71375059953485</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-36.53314495747961,174.7135318051336</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>-36.53384492730803,174.71360868809066</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
